--- a/Examples/Powder_Raman/QE/results.ref.xlsx
+++ b/Examples/Powder_Raman/QE/results.ref.xlsx
@@ -130,13 +130,13 @@
     <t>Absorption maximum (L/mole/cm)</t>
   </si>
   <si>
-    <t>Raman R_total (Å4/amu)</t>
+    <t>Raman R_total (Å⁴/amu)</t>
   </si>
   <si>
-    <t>Raman R_parallel (Å4/amu)</t>
+    <t>Raman R_parallel (Å⁴/amu)</t>
   </si>
   <si>
-    <t>Raman R_perp (Å4/amu)</t>
+    <t>Raman R_perp (Å⁴/amu)</t>
   </si>
   <si>
     <t>No</t>
@@ -1142,13 +1142,13 @@
         <v>0.0102795051158248</v>
       </c>
       <c r="I26">
-        <v>0.7611459598619388</v>
+        <v>0.2373255982197894</v>
       </c>
       <c r="J26">
-        <v>0.4349416296053052</v>
+        <v>0.1356149646455357</v>
       </c>
       <c r="K26">
-        <v>0.3262043302566335</v>
+        <v>0.1017106335742538</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1174,13 +1174,13 @@
         <v>0.002545148861712588</v>
       </c>
       <c r="I27">
-        <v>34.32480609518199</v>
+        <v>10.70248752525066</v>
       </c>
       <c r="J27">
-        <v>21.51518450361923</v>
+        <v>6.708442667233959</v>
       </c>
       <c r="K27">
-        <v>12.80962159156276</v>
+        <v>3.994044858016702</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1206,13 +1206,13 @@
         <v>0.007783196661757761</v>
       </c>
       <c r="I28">
-        <v>11.59391071794426</v>
+        <v>3.614985747729699</v>
       </c>
       <c r="J28">
-        <v>7.238648709747707</v>
+        <v>2.257013406016616</v>
       </c>
       <c r="K28">
-        <v>4.355262008196554</v>
+        <v>1.357972341713082</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1238,13 +1238,13 @@
         <v>7.313140611245422E-28</v>
       </c>
       <c r="I29">
-        <v>0.2567381457427003</v>
+        <v>0.08005105096436138</v>
       </c>
       <c r="J29">
-        <v>0.1467075118529716</v>
+        <v>0.04574345769392078</v>
       </c>
       <c r="K29">
-        <v>0.1100306338897287</v>
+        <v>0.03430759327044058</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1270,13 +1270,13 @@
         <v>8.860584016866135E-28</v>
       </c>
       <c r="I30">
-        <v>0.2567381455829664</v>
+        <v>0.08005105091455629</v>
       </c>
       <c r="J30">
-        <v>0.1467075117616951</v>
+        <v>0.04574345766546074</v>
       </c>
       <c r="K30">
-        <v>0.1100306338212713</v>
+        <v>0.03430759324909555</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1302,13 +1302,13 @@
         <v>2.373763037639138E-27</v>
       </c>
       <c r="I31">
-        <v>3.393458617538513E-29</v>
+        <v>1.058081680664123E-29</v>
       </c>
       <c r="J31">
-        <v>1.939119210022008E-29</v>
+        <v>6.046181032366417E-30</v>
       </c>
       <c r="K31">
-        <v>1.454339407516506E-29</v>
+        <v>4.534635774274813E-30</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1334,13 +1334,13 @@
         <v>8865.01943466225</v>
       </c>
       <c r="I32">
-        <v>64.2882830414748</v>
+        <v>20.04511097202513</v>
       </c>
       <c r="J32">
-        <v>36.7361617379856</v>
+        <v>11.4543491268715</v>
       </c>
       <c r="K32">
-        <v>27.5521213034892</v>
+        <v>8.590761845153628</v>
       </c>
     </row>
     <row r="33" spans="2:11">
@@ -1366,13 +1366,13 @@
         <v>8865.019455817457</v>
       </c>
       <c r="I33">
-        <v>64.28828312160267</v>
+        <v>20.04511099700903</v>
       </c>
       <c r="J33">
-        <v>36.73616178377296</v>
+        <v>11.45434914114802</v>
       </c>
       <c r="K33">
-        <v>27.55212133782972</v>
+        <v>8.590761855861015</v>
       </c>
     </row>
     <row r="34" spans="2:11">
@@ -1398,13 +1398,13 @@
         <v>9278.875746837861</v>
       </c>
       <c r="I34">
-        <v>674.4254991791938</v>
+        <v>210.2861257733203</v>
       </c>
       <c r="J34">
-        <v>388.1308877615244</v>
+        <v>121.019357630552</v>
       </c>
       <c r="K34">
-        <v>286.2946114176694</v>
+        <v>89.26676814276833</v>
       </c>
     </row>
     <row r="35" spans="2:11">
@@ -1430,13 +1430,13 @@
         <v>1.074565771809325E-26</v>
       </c>
       <c r="I35">
-        <v>267.8922440630895</v>
+        <v>83.52890304015627</v>
       </c>
       <c r="J35">
-        <v>153.0812823217655</v>
+        <v>47.73080173723216</v>
       </c>
       <c r="K35">
-        <v>114.8109617413241</v>
+        <v>35.79810130292412</v>
       </c>
     </row>
     <row r="36" spans="2:11">
@@ -1462,13 +1462,13 @@
         <v>1.888142461461067E-26</v>
       </c>
       <c r="I36">
-        <v>267.8922438960055</v>
+        <v>83.52890298805941</v>
       </c>
       <c r="J36">
-        <v>153.0812822262889</v>
+        <v>47.73080170746251</v>
       </c>
       <c r="K36">
-        <v>114.8109616697166</v>
+        <v>35.79810128059689</v>
       </c>
     </row>
     <row r="37" spans="2:11">
@@ -1494,13 +1494,13 @@
         <v>4.169305487387134E-28</v>
       </c>
       <c r="I37">
-        <v>4.651826390953378E-29</v>
+        <v>1.450441228444363E-29</v>
       </c>
       <c r="J37">
-        <v>2.700446914753056E-29</v>
+        <v>8.42000369575372E-30</v>
       </c>
       <c r="K37">
-        <v>1.951379476200322E-29</v>
+        <v>6.084408588689913E-30</v>
       </c>
     </row>
   </sheetData>
